--- a/data/trans_bre/P19C07-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P19C07-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 2,44</t>
+          <t>-1,03; 2,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,39</t>
+          <t>-1,16; 1,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 3,2</t>
+          <t>-0,24; 3,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,9</t>
+          <t>-1,41; 2,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,18; 136,06</t>
+          <t>-30,49; 133,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-46,72; 133,49</t>
+          <t>-48,39; 146,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-14,24; 619,07</t>
+          <t>-20,56; 505,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-40,47; 140,72</t>
+          <t>-39,65; 150,84</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,45</t>
+          <t>-1,58; 1,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 2,34</t>
+          <t>-0,62; 2,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,63</t>
+          <t>-0,94; 1,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 2,05</t>
+          <t>-1,19; 2,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,71; 43,81</t>
+          <t>-32,89; 38,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,73; 73,06</t>
+          <t>-14,16; 75,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,96; 57,02</t>
+          <t>-22,75; 55,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,4; 83,37</t>
+          <t>-29,23; 85,92</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,36</t>
+          <t>-3,35; 1,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 2,88</t>
+          <t>-2,61; 2,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 3,57</t>
+          <t>-0,42; 3,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 4,56</t>
+          <t>-0,06; 4,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-74,74; 91,54</t>
+          <t>-77,46; 64,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-53,01; 97,13</t>
+          <t>-47,49; 88,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-29,58; 359,95</t>
+          <t>-28,04; 389,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 202,17</t>
+          <t>-2,07; 212,28</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,0</t>
+          <t>-0,96; 1,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,21</t>
+          <t>-0,71; 1,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 1,68</t>
+          <t>-0,25; 1,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,82</t>
+          <t>-0,47; 1,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,78; 33,87</t>
+          <t>-24,1; 36,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,58; 41,62</t>
+          <t>-18,25; 41,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 68,45</t>
+          <t>-7,52; 70,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 73,06</t>
+          <t>-11,94; 70,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C07-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P19C07-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>36,52%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 2,32</t>
+          <t>-0,73; 2,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,43</t>
+          <t>-1,13; 1,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 3,25</t>
+          <t>-0,09; 3,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 2,02</t>
+          <t>-0,91; 2,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-30,49; 133,5</t>
+          <t>-23,15; 146,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-48,39; 146,38</t>
+          <t>-43,81; 134,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,56; 505,62</t>
+          <t>-10,79; 527,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,65; 150,84</t>
+          <t>-27,3; 166,36</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,33</t>
+          <t>-1,62; 1,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 2,37</t>
+          <t>-0,71; 2,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 1,64</t>
+          <t>-0,99; 1,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 2,07</t>
+          <t>-0,9; 1,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,89; 38,87</t>
+          <t>-33,32; 42,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 75,42</t>
+          <t>-16,19; 73,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,75; 55,71</t>
+          <t>-22,49; 55,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,23; 85,92</t>
+          <t>-21,01; 59,26</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,14</t>
+          <t>1,93</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>62,46%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 1,11</t>
+          <t>-3,17; 1,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 2,72</t>
+          <t>-2,74; 3,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 3,56</t>
+          <t>-0,42; 3,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 4,39</t>
+          <t>-0,19; 4,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-77,46; 64,69</t>
+          <t>-75,96; 72,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-47,49; 88,87</t>
+          <t>-49,47; 96,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-28,04; 389,35</t>
+          <t>-26,0; 362,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 212,28</t>
+          <t>-8,4; 186,04</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,7</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,07%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,07</t>
+          <t>-0,98; 1,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 1,21</t>
+          <t>-0,73; 1,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,67</t>
+          <t>-0,35; 1,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,81</t>
+          <t>-0,21; 1,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,1; 36,01</t>
+          <t>-24,35; 39,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 41,59</t>
+          <t>-18,96; 43,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 70,72</t>
+          <t>-11,37; 68,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 70,14</t>
+          <t>-5,74; 64,73</t>
         </is>
       </c>
     </row>
